--- a/template/employee_report_template.xlsx
+++ b/template/employee_report_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ythsi\Pycharm\AttendanceProject\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38337295-D69B-4BCB-8E43-216745C03BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{372D8802-C443-4652-991D-BBE1759D4EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AEB25E42-977A-4128-95ED-AE51CD6399DB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
   <si>
     <t>LATE IN</t>
   </si>
@@ -144,6 +144,12 @@
   </si>
   <si>
     <t>MANUAL OT</t>
+  </si>
+  <si>
+    <t>FINAL Agreed and Approved by HR</t>
+  </si>
+  <si>
+    <t>人力資源部同意並批准</t>
   </si>
 </sst>
 </file>
@@ -444,7 +450,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -590,12 +596,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -610,6 +610,21 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1029,10 +1044,10 @@
   <sheetData>
     <row r="1" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="62"/>
+      <c r="C1" s="60"/>
       <c r="D1" s="43"/>
       <c r="E1" s="26" t="s">
         <v>1</v>
@@ -1047,7 +1062,9 @@
       </c>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
+      <c r="N1" s="63" t="s">
+        <v>36</v>
+      </c>
       <c r="O1" s="3"/>
       <c r="P1" s="2"/>
       <c r="R1" s="2" t="s">
@@ -1056,10 +1073,10 @@
     </row>
     <row r="2" spans="1:18" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="62"/>
+      <c r="C2" s="60"/>
       <c r="D2" s="43"/>
       <c r="E2" s="27" t="s">
         <v>6</v>
@@ -1074,7 +1091,9 @@
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
+      <c r="N2" s="63" t="s">
+        <v>37</v>
+      </c>
       <c r="O2" s="3"/>
       <c r="P2" s="2"/>
       <c r="R2" s="2" t="s">
@@ -1083,10 +1102,10 @@
     </row>
     <row r="3" spans="1:18" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4"/>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="62"/>
+      <c r="C3" s="60"/>
       <c r="D3" s="46"/>
       <c r="E3" s="42" t="s">
         <v>13</v>
@@ -1106,10 +1125,10 @@
     </row>
     <row r="4" spans="1:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4"/>
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="62"/>
+      <c r="C4" s="60"/>
       <c r="D4" s="46"/>
       <c r="E4" s="41"/>
       <c r="F4" s="5"/>
@@ -1139,11 +1158,11 @@
       <c r="J5" s="24"/>
       <c r="K5" s="6"/>
       <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
+      <c r="M5" s="62"/>
+      <c r="N5" s="6"/>
       <c r="O5" s="7"/>
       <c r="P5" s="6"/>
-      <c r="Q5" s="2"/>
+      <c r="Q5" s="62"/>
       <c r="R5" s="2"/>
     </row>
     <row r="6" spans="1:18" ht="21" x14ac:dyDescent="0.35">
@@ -1160,7 +1179,9 @@
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
+      <c r="N6" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="O6" s="3"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
@@ -1198,10 +1219,10 @@
       <c r="A9" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="59"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
       <c r="F9" s="14"/>
       <c r="G9" s="15" t="s">
         <v>18</v>
@@ -1221,8 +1242,8 @@
       <c r="P9" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="Q9" s="63"/>
-      <c r="R9" s="63"/>
+      <c r="Q9" s="61"/>
+      <c r="R9" s="61"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
@@ -1310,7 +1331,7 @@
       <c r="O12" s="54"/>
       <c r="P12" s="36"/>
       <c r="Q12" s="23"/>
-      <c r="R12" s="57"/>
+      <c r="R12" s="64"/>
     </row>
     <row r="13" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A13" s="21"/>
@@ -1330,7 +1351,7 @@
       <c r="O13" s="54"/>
       <c r="P13" s="36"/>
       <c r="Q13" s="23"/>
-      <c r="R13" s="58"/>
+      <c r="R13" s="65"/>
     </row>
     <row r="14" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A14" s="21"/>
@@ -1350,7 +1371,7 @@
       <c r="O14" s="40"/>
       <c r="P14" s="36"/>
       <c r="Q14" s="23"/>
-      <c r="R14" s="58"/>
+      <c r="R14" s="65"/>
     </row>
     <row r="15" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A15" s="21"/>
@@ -1370,7 +1391,7 @@
       <c r="O15" s="40"/>
       <c r="P15" s="36"/>
       <c r="Q15" s="23"/>
-      <c r="R15" s="58"/>
+      <c r="R15" s="65"/>
     </row>
     <row r="16" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A16" s="21"/>
@@ -1390,7 +1411,7 @@
       <c r="O16" s="55"/>
       <c r="P16" s="36"/>
       <c r="Q16" s="23"/>
-      <c r="R16" s="58"/>
+      <c r="R16" s="65"/>
     </row>
     <row r="17" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A17" s="21"/>
@@ -1410,7 +1431,7 @@
       <c r="O17" s="40"/>
       <c r="P17" s="40"/>
       <c r="Q17" s="23"/>
-      <c r="R17" s="58"/>
+      <c r="R17" s="65"/>
     </row>
     <row r="18" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A18" s="21"/>
@@ -1430,7 +1451,7 @@
       <c r="O18" s="55"/>
       <c r="P18" s="36"/>
       <c r="Q18" s="23"/>
-      <c r="R18" s="58"/>
+      <c r="R18" s="65"/>
     </row>
     <row r="19" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A19" s="21"/>
@@ -1450,7 +1471,7 @@
       <c r="O19" s="40"/>
       <c r="P19" s="36"/>
       <c r="Q19" s="23"/>
-      <c r="R19" s="58"/>
+      <c r="R19" s="65"/>
     </row>
     <row r="20" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A20" s="21"/>
@@ -1470,7 +1491,7 @@
       <c r="O20" s="40"/>
       <c r="P20" s="36"/>
       <c r="Q20" s="23"/>
-      <c r="R20" s="58"/>
+      <c r="R20" s="65"/>
     </row>
     <row r="21" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A21" s="21"/>
@@ -1490,7 +1511,7 @@
       <c r="O21" s="55"/>
       <c r="P21" s="36"/>
       <c r="Q21" s="23"/>
-      <c r="R21" s="58"/>
+      <c r="R21" s="65"/>
     </row>
     <row r="22" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A22" s="21"/>
@@ -1510,7 +1531,7 @@
       <c r="O22" s="54"/>
       <c r="P22" s="36"/>
       <c r="Q22" s="23"/>
-      <c r="R22" s="58"/>
+      <c r="R22" s="65"/>
     </row>
     <row r="23" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A23" s="21"/>
@@ -1530,7 +1551,7 @@
       <c r="O23" s="40"/>
       <c r="P23" s="36"/>
       <c r="Q23" s="23"/>
-      <c r="R23" s="58"/>
+      <c r="R23" s="65"/>
     </row>
     <row r="24" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A24" s="21"/>
@@ -1550,7 +1571,7 @@
       <c r="O24" s="40"/>
       <c r="P24" s="36"/>
       <c r="Q24" s="23"/>
-      <c r="R24" s="58"/>
+      <c r="R24" s="65"/>
     </row>
     <row r="25" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A25" s="21"/>
@@ -1570,7 +1591,7 @@
       <c r="O25" s="55"/>
       <c r="P25" s="40"/>
       <c r="Q25" s="23"/>
-      <c r="R25" s="58"/>
+      <c r="R25" s="65"/>
     </row>
     <row r="26" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A26" s="21"/>
@@ -1590,7 +1611,7 @@
       <c r="O26" s="40"/>
       <c r="P26" s="36"/>
       <c r="Q26" s="23"/>
-      <c r="R26" s="58"/>
+      <c r="R26" s="65"/>
     </row>
     <row r="27" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A27" s="21"/>
@@ -1610,7 +1631,7 @@
       <c r="O27" s="55"/>
       <c r="P27" s="36"/>
       <c r="Q27" s="23"/>
-      <c r="R27" s="58"/>
+      <c r="R27" s="65"/>
     </row>
     <row r="28" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A28" s="21"/>
@@ -1630,7 +1651,7 @@
       <c r="O28" s="40"/>
       <c r="P28" s="36"/>
       <c r="Q28" s="23"/>
-      <c r="R28" s="58"/>
+      <c r="R28" s="65"/>
     </row>
     <row r="29" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A29" s="21"/>
@@ -1650,7 +1671,7 @@
       <c r="O29" s="55"/>
       <c r="P29" s="36"/>
       <c r="Q29" s="23"/>
-      <c r="R29" s="58"/>
+      <c r="R29" s="65"/>
     </row>
     <row r="30" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A30" s="21"/>
@@ -1670,7 +1691,7 @@
       <c r="O30" s="40"/>
       <c r="P30" s="36"/>
       <c r="Q30" s="23"/>
-      <c r="R30" s="58"/>
+      <c r="R30" s="65"/>
     </row>
     <row r="31" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A31" s="21"/>
@@ -1690,7 +1711,7 @@
       <c r="O31" s="40"/>
       <c r="P31" s="36"/>
       <c r="Q31" s="23"/>
-      <c r="R31" s="58"/>
+      <c r="R31" s="65"/>
     </row>
     <row r="32" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A32" s="21"/>
@@ -1710,7 +1731,7 @@
       <c r="O32" s="40"/>
       <c r="P32" s="36"/>
       <c r="Q32" s="23"/>
-      <c r="R32" s="58"/>
+      <c r="R32" s="65"/>
     </row>
     <row r="33" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A33" s="21"/>
@@ -1730,7 +1751,7 @@
       <c r="O33" s="40"/>
       <c r="P33" s="40"/>
       <c r="Q33" s="23"/>
-      <c r="R33" s="58"/>
+      <c r="R33" s="65"/>
     </row>
     <row r="34" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A34" s="21"/>
@@ -1750,7 +1771,7 @@
       <c r="O34" s="55"/>
       <c r="P34" s="36"/>
       <c r="Q34" s="23"/>
-      <c r="R34" s="58"/>
+      <c r="R34" s="65"/>
     </row>
     <row r="35" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A35" s="21"/>
@@ -1770,7 +1791,7 @@
       <c r="O35" s="54"/>
       <c r="P35" s="36"/>
       <c r="Q35" s="23"/>
-      <c r="R35" s="58"/>
+      <c r="R35" s="65"/>
     </row>
     <row r="36" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A36" s="21"/>
@@ -1790,7 +1811,7 @@
       <c r="O36" s="40"/>
       <c r="P36" s="36"/>
       <c r="Q36" s="23"/>
-      <c r="R36" s="58"/>
+      <c r="R36" s="65"/>
     </row>
     <row r="37" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A37" s="21"/>
@@ -1810,7 +1831,7 @@
       <c r="O37" s="40"/>
       <c r="P37" s="36"/>
       <c r="Q37" s="23"/>
-      <c r="R37" s="58"/>
+      <c r="R37" s="65"/>
     </row>
     <row r="38" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A38" s="21"/>
@@ -1830,7 +1851,7 @@
       <c r="O38" s="55"/>
       <c r="P38" s="36"/>
       <c r="Q38" s="23"/>
-      <c r="R38" s="58"/>
+      <c r="R38" s="65"/>
     </row>
     <row r="39" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A39" s="21"/>
@@ -1850,7 +1871,7 @@
       <c r="O39" s="40"/>
       <c r="P39" s="36"/>
       <c r="Q39" s="23"/>
-      <c r="R39" s="58"/>
+      <c r="R39" s="65"/>
     </row>
     <row r="40" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A40" s="21"/>
@@ -1870,7 +1891,7 @@
       <c r="O40" s="40"/>
       <c r="P40" s="36"/>
       <c r="Q40" s="23"/>
-      <c r="R40" s="58"/>
+      <c r="R40" s="65"/>
     </row>
     <row r="41" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A41" s="21"/>
@@ -1890,7 +1911,7 @@
       <c r="O41" s="40"/>
       <c r="P41" s="40"/>
       <c r="Q41" s="23"/>
-      <c r="R41" s="58"/>
+      <c r="R41" s="65"/>
     </row>
     <row r="42" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A42" s="21"/>
@@ -1910,7 +1931,7 @@
       <c r="O42" s="40"/>
       <c r="P42" s="36"/>
       <c r="Q42" s="23"/>
-      <c r="R42" s="58"/>
+      <c r="R42" s="65"/>
     </row>
     <row r="43" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A43" s="21"/>
@@ -1930,7 +1951,7 @@
       <c r="O43" s="40"/>
       <c r="P43" s="36"/>
       <c r="Q43" s="23"/>
-      <c r="R43" s="58"/>
+      <c r="R43" s="65"/>
     </row>
     <row r="44" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A44" s="21"/>
@@ -1950,7 +1971,7 @@
       <c r="O44" s="40"/>
       <c r="P44" s="36"/>
       <c r="Q44" s="23"/>
-      <c r="R44" s="58"/>
+      <c r="R44" s="65"/>
     </row>
     <row r="45" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A45" s="21"/>
@@ -1970,7 +1991,7 @@
       <c r="O45" s="40"/>
       <c r="P45" s="36"/>
       <c r="Q45" s="23"/>
-      <c r="R45" s="58"/>
+      <c r="R45" s="65"/>
     </row>
     <row r="46" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A46" s="21"/>
@@ -1990,7 +2011,7 @@
       <c r="O46" s="55"/>
       <c r="P46" s="36"/>
       <c r="Q46" s="23"/>
-      <c r="R46" s="58"/>
+      <c r="R46" s="65"/>
     </row>
     <row r="47" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A47" s="23"/>
@@ -2010,7 +2031,7 @@
       <c r="O47" s="40"/>
       <c r="P47" s="40"/>
       <c r="Q47" s="30"/>
-      <c r="R47" s="58"/>
+      <c r="R47" s="65"/>
     </row>
     <row r="48" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A48" s="23"/>
@@ -2030,7 +2051,7 @@
       <c r="O48" s="40"/>
       <c r="P48" s="40"/>
       <c r="Q48" s="30"/>
-      <c r="R48" s="58"/>
+      <c r="R48" s="65"/>
     </row>
     <row r="49" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A49" s="23"/>
@@ -2050,7 +2071,7 @@
       <c r="O49" s="40"/>
       <c r="P49" s="40"/>
       <c r="Q49" s="30"/>
-      <c r="R49" s="58"/>
+      <c r="R49" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="7">
